--- a/business_forms/033_equipment_rental_authorization_form--business_forms.xlsx
+++ b/business_forms/033_equipment_rental_authorization_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>equipment_type_1</t>
+          <t>equipment type 1</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>equipment_type_2</t>
+          <t>equipment type 2</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rental_term_1</t>
+          <t>rental term 1</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rental_term_2</t>
+          <t>rental term 2</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rental_term_3</t>
+          <t>rental term 3</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rental_term_4</t>
+          <t>rental term 4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rental_term_5</t>
+          <t>rental term 5</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>equipment_status_1</t>
+          <t>equipment status 1</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>equipment_status_2</t>
+          <t>equipment status 2</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>equipment_status_3</t>
+          <t>equipment status 3</t>
         </is>
       </c>
     </row>
